--- a/data/trans_orig/Q23_tabaco_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2007</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2007 (tasa de respuesta: 86,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>249859</t>
+          <t>248971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>297769</t>
+          <t>297815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41474</t>
+          <t>42232</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67269</t>
+          <t>66489</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>302978</t>
+          <t>302280</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>356968</t>
+          <t>357205</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,66%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>292522</t>
+          <t>292476</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>340432</t>
+          <t>341320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142339</t>
+          <t>143119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>168134</t>
+          <t>167376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>442932</t>
+          <t>442695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>496922</t>
+          <t>497620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>263504</t>
+          <t>262783</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>320553</t>
+          <t>317743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>157934</t>
+          <t>158446</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204144</t>
+          <t>204070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>432968</t>
+          <t>434643</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>503240</t>
+          <t>503535</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>575664</t>
+          <t>578474</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>632713</t>
+          <t>633434</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>415485</t>
+          <t>415559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>461695</t>
+          <t>461183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1012607</t>
+          <t>1012312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1082879</t>
+          <t>1081204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33664</t>
+          <t>33785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59164</t>
+          <t>57955</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>39077</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57053</t>
+          <t>58398</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89884</t>
+          <t>88769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>175391</t>
+          <t>176600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200891</t>
+          <t>200770</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130670</t>
+          <t>130049</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>150657</t>
+          <t>150305</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>313797</t>
+          <t>314912</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>346628</t>
+          <t>345283</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>568525</t>
+          <t>572225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>647867</t>
+          <t>650850</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>236687</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>292305</t>
+          <t>292311</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>816937</t>
+          <t>820550</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>916984</t>
+          <t>919160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1073197</t>
+          <t>1070214</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1152539</t>
+          <t>1148839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706059</t>
+          <t>706053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>761677</t>
+          <t>763423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1802443</t>
+          <t>1800267</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1902490</t>
+          <t>1898877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2012</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2012 (tasa de respuesta: 94,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>285145</t>
+          <t>285226</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>336453</t>
+          <t>337708</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66895</t>
+          <t>65947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98472</t>
+          <t>97263</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>367328</t>
+          <t>364873</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>427695</t>
+          <t>427402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>342219</t>
+          <t>340964</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393527</t>
+          <t>393446</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>164798</t>
+          <t>166007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>196375</t>
+          <t>197323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514246</t>
+          <t>514539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>574613</t>
+          <t>577068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>61,26%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>341163</t>
+          <t>338514</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>406944</t>
+          <t>404797</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>220253</t>
+          <t>217665</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>274932</t>
+          <t>273959</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>575785</t>
+          <t>577024</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>659702</t>
+          <t>663687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>713599</t>
+          <t>715746</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>779380</t>
+          <t>782029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>573091</t>
+          <t>574064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>627770</t>
+          <t>630358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1308864</t>
+          <t>1304879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1392781</t>
+          <t>1391542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,69%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35495</t>
+          <t>35174</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63162</t>
+          <t>61674</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26495</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51683</t>
+          <t>53276</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69835</t>
+          <t>68799</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105956</t>
+          <t>104742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178355</t>
+          <t>179843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206022</t>
+          <t>206343</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>154456</t>
+          <t>152863</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179644</t>
+          <t>178588</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>341700</t>
+          <t>342914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>377821</t>
+          <t>378857</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,63%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>684862</t>
+          <t>688022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>777515</t>
+          <t>782753</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>331091</t>
+          <t>331337</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>401390</t>
+          <t>402629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1039640</t>
+          <t>1035795</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1149899</t>
+          <t>1151495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1263218</t>
+          <t>1257980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1355871</t>
+          <t>1352711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>916041</t>
+          <t>914802</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>986340</t>
+          <t>986094</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2208264</t>
+          <t>2206668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2318523</t>
+          <t>2322368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2016</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>175173</t>
+          <t>174610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>216402</t>
+          <t>214334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>45472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71132</t>
+          <t>70711</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>229916</t>
+          <t>228065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>277018</t>
+          <t>278014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>46,28%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>211331</t>
+          <t>213399</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>252560</t>
+          <t>253123</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101917</t>
+          <t>102338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127683</t>
+          <t>127577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>323763</t>
+          <t>322767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>370865</t>
+          <t>372716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>62,04%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>354283</t>
+          <t>358427</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>421990</t>
+          <t>423288</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>191457</t>
+          <t>189284</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240068</t>
+          <t>240951</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>563040</t>
+          <t>564159</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>642162</t>
+          <t>646084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>684551</t>
+          <t>683253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>752258</t>
+          <t>748114</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608473</t>
+          <t>607590</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>657084</t>
+          <t>659257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1312920</t>
+          <t>1308998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1392042</t>
+          <t>1390923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,14%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39494</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68159</t>
+          <t>68544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36192</t>
+          <t>37078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62588</t>
+          <t>62722</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84483</t>
+          <t>84261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121087</t>
+          <t>122666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,05%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152589</t>
+          <t>152204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181254</t>
+          <t>180441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153930</t>
+          <t>153796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180326</t>
+          <t>179440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>316180</t>
+          <t>314601</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352784</t>
+          <t>353006</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,73%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>592734</t>
+          <t>593427</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>674617</t>
+          <t>674271</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>291594</t>
+          <t>289723</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>353450</t>
+          <t>353981</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>897120</t>
+          <t>902029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1007602</t>
+          <t>1011252</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,79%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1080405</t>
+          <t>1080751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1162288</t>
+          <t>1161595</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>884658</t>
+          <t>884127</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>946514</t>
+          <t>948385</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1985528</t>
+          <t>1981878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2096010</t>
+          <t>2091101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2023</t>
+          <t>Población cuyo inicio en el consumo de tabaco fue antes de los 15 años en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145477</t>
+          <t>145810</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177608</t>
+          <t>178798</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24988</t>
+          <t>24856</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40416</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>176280</t>
+          <t>174818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>211955</t>
+          <t>212180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>123304</t>
+          <t>122114</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155435</t>
+          <t>155102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76743</t>
+          <t>77358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92171</t>
+          <t>92303</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>206116</t>
+          <t>205891</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>241791</t>
+          <t>243253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,18%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148549</t>
+          <t>149402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>365816</t>
+          <t>366988</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>141122</t>
+          <t>142819</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>182347</t>
+          <t>183656</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>269085</t>
+          <t>268333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>520168</t>
+          <t>524979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>763045</t>
+          <t>761873</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>980312</t>
+          <t>979459</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>476886</t>
+          <t>475577</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>518111</t>
+          <t>516414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1267927</t>
+          <t>1263116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1519010</t>
+          <t>1519762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,99%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36724</t>
+          <t>35583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59634</t>
+          <t>60260</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31639</t>
+          <t>32408</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52136</t>
+          <t>52094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72084</t>
+          <t>73657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104902</t>
+          <t>105901</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>177521</t>
+          <t>176895</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200431</t>
+          <t>201572</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141074</t>
+          <t>141116</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>161571</t>
+          <t>160802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>325463</t>
+          <t>324464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>358281</t>
+          <t>356708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>298395</t>
+          <t>294204</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>583959</t>
+          <t>587316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>211774</t>
+          <t>209671</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>257936</t>
+          <t>258198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>515318</t>
+          <t>549260</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>813850</t>
+          <t>809727</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1082969</t>
+          <t>1079612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1368533</t>
+          <t>1372724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711667</t>
+          <t>711405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>757829</t>
+          <t>759932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1822680</t>
+          <t>1826803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2121212</t>
+          <t>2087270</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>79,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q23_tabaco_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>248971</t>
+          <t>251498</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>297815</t>
+          <t>300354</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42232</t>
+          <t>42455</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66489</t>
+          <t>69010</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>302280</t>
+          <t>302439</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>292476</t>
+          <t>289937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>341320</t>
+          <t>338793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143119</t>
+          <t>140598</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>167153</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>497620</t>
+          <t>497461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>262783</t>
+          <t>260929</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>317743</t>
+          <t>316760</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>158446</t>
+          <t>160613</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>204070</t>
+          <t>205518</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>434643</t>
+          <t>436596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>503535</t>
+          <t>505075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>578474</t>
+          <t>579457</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>633434</t>
+          <t>635288</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>415559</t>
+          <t>414111</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>461183</t>
+          <t>459016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1012312</t>
+          <t>1010772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1081204</t>
+          <t>1079251</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33785</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57955</t>
+          <t>59081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,82 +1434,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>27477</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18736</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>39306</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>16,25%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>23,24%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>72562</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>58110</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>90310</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>17,98%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>14,4%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>27477</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>18821</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>39077</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,25%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>11,13%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>23,11%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>72562</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>58398</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>88769</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>17,98%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>176600</t>
+          <t>175474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>200770</t>
+          <t>201706</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,82 +1547,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>86,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>141649</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>129820</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>150390</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>83,75%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>76,76%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>331119</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>313371</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>345571</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>82,02%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>77,63%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>85,6%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141649</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>130049</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>150305</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>76,89%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>88,87%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>331119</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>314912</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>345283</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>82,02%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>78,01%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>572225</t>
+          <t>567441</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>650850</t>
+          <t>653171</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>234941</t>
+          <t>234847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>292311</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>820550</t>
+          <t>821881</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>919160</t>
+          <t>921289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1070214</t>
+          <t>1067893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1148839</t>
+          <t>1153623</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>706053</t>
+          <t>708290</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>763423</t>
+          <t>763517</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1800267</t>
+          <t>1798138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1898877</t>
+          <t>1897546</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>285226</t>
+          <t>286662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>337708</t>
+          <t>337176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>65947</t>
+          <t>65631</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97263</t>
+          <t>97200</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>364873</t>
+          <t>360504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>427402</t>
+          <t>424188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>340964</t>
+          <t>341496</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393446</t>
+          <t>392010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,97%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166007</t>
+          <t>166070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197323</t>
+          <t>197639</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>514539</t>
+          <t>517753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577068</t>
+          <t>581437</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,73%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>338514</t>
+          <t>339079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>404797</t>
+          <t>405423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>217665</t>
+          <t>216377</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>273959</t>
+          <t>273543</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>577024</t>
+          <t>574698</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>663687</t>
+          <t>662419</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>715746</t>
+          <t>715120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>782029</t>
+          <t>781464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>574064</t>
+          <t>574480</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>630358</t>
+          <t>631646</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1304879</t>
+          <t>1306147</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1391542</t>
+          <t>1393868</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35174</t>
+          <t>35568</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>61265</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53276</t>
+          <t>52385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68799</t>
+          <t>70242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>104742</t>
+          <t>109267</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179843</t>
+          <t>180252</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206343</t>
+          <t>205949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>152863</t>
+          <t>153754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>178588</t>
+          <t>178123</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>342914</t>
+          <t>338389</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378857</t>
+          <t>377414</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,31%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>688022</t>
+          <t>687633</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>782753</t>
+          <t>776008</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>331337</t>
+          <t>331478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>402629</t>
+          <t>400047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1035795</t>
+          <t>1039296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1151495</t>
+          <t>1151292</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1257980</t>
+          <t>1264725</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1352711</t>
+          <t>1353100</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>914802</t>
+          <t>917384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>986094</t>
+          <t>985953</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2206668</t>
+          <t>2206871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2322368</t>
+          <t>2318867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>174610</t>
+          <t>174428</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>214334</t>
+          <t>215036</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45472</t>
+          <t>45008</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70711</t>
+          <t>71471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>228065</t>
+          <t>227110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278014</t>
+          <t>276107</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>213399</t>
+          <t>212697</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>253123</t>
+          <t>253305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102338</t>
+          <t>101578</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127577</t>
+          <t>128041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>322767</t>
+          <t>324674</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>372716</t>
+          <t>373671</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,2%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>358427</t>
+          <t>358998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>423288</t>
+          <t>422265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189284</t>
+          <t>190918</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>240951</t>
+          <t>239787</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>564159</t>
+          <t>559614</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>646084</t>
+          <t>642457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>683253</t>
+          <t>684276</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>748114</t>
+          <t>747543</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>607590</t>
+          <t>608754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>659257</t>
+          <t>657623</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1308998</t>
+          <t>1312625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1390923</t>
+          <t>1395468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,38%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40307</t>
+          <t>39981</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68544</t>
+          <t>68325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37078</t>
+          <t>37027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62722</t>
+          <t>63487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84261</t>
+          <t>85697</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122666</t>
+          <t>122718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152204</t>
+          <t>152423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180441</t>
+          <t>180767</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153796</t>
+          <t>153031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179440</t>
+          <t>179491</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314601</t>
+          <t>314549</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>353006</t>
+          <t>351570</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,4%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>593427</t>
+          <t>596034</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>674271</t>
+          <t>677659</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>289723</t>
+          <t>289412</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>353981</t>
+          <t>350416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>902029</t>
+          <t>905658</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1011252</t>
+          <t>1013617</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1080751</t>
+          <t>1077363</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1161595</t>
+          <t>1158988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>884127</t>
+          <t>887692</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>948385</t>
+          <t>948696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1981878</t>
+          <t>1979513</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2091101</t>
+          <t>2087472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,74%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>161593</t>
+          <t>170168</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145810</t>
+          <t>152241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178798</t>
+          <t>187254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32050</t>
+          <t>34186</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>26450</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39801</t>
+          <t>43387</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>193643</t>
+          <t>204354</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>174818</t>
+          <t>185308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212180</t>
+          <t>224408</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>49,98%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>139319</t>
+          <t>152152</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>122114</t>
+          <t>135066</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155102</t>
+          <t>170079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85109</t>
+          <t>92510</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77358</t>
+          <t>83309</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92303</t>
+          <t>100246</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>224428</t>
+          <t>244662</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205891</t>
+          <t>224608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>243253</t>
+          <t>263708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,73%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>300912</t>
+          <t>322320</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>300912</t>
+          <t>322320</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>300912</t>
+          <t>322320</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>126696</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>126696</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>126696</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>418071</t>
+          <t>449016</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>418071</t>
+          <t>449016</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>418071</t>
+          <t>449016</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>277869</t>
+          <t>297329</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>149402</t>
+          <t>264567</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>366988</t>
+          <t>331320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>161820</t>
+          <t>169881</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>142819</t>
+          <t>150769</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183656</t>
+          <t>191658</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>439688</t>
+          <t>467210</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>268333</t>
+          <t>429765</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>524979</t>
+          <t>503118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>850992</t>
+          <t>668721</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>761873</t>
+          <t>634730</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>979459</t>
+          <t>701483</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>69,22%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>497413</t>
+          <t>545811</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>475577</t>
+          <t>524034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>516414</t>
+          <t>564923</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1348407</t>
+          <t>1214532</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1263116</t>
+          <t>1178624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1519762</t>
+          <t>1251977</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>74,45%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1128861</t>
+          <t>966050</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1128861</t>
+          <t>966050</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1128861</t>
+          <t>966050</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>659233</t>
+          <t>715692</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>659233</t>
+          <t>715692</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>659233</t>
+          <t>715692</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1788095</t>
+          <t>1681742</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1788095</t>
+          <t>1681742</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1788095</t>
+          <t>1681742</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>50840</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35583</t>
+          <t>39259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60260</t>
+          <t>64155</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>43072</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32408</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52094</t>
+          <t>53723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>88442</t>
+          <t>93912</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73657</t>
+          <t>78315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105901</t>
+          <t>112256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>189268</t>
+          <t>203654</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>176895</t>
+          <t>190339</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>201572</t>
+          <t>215235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>152656</t>
+          <t>167937</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>141116</t>
+          <t>157286</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160802</t>
+          <t>176667</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>341923</t>
+          <t>371591</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>324464</t>
+          <t>353247</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>356708</t>
+          <t>387188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>237155</t>
+          <t>254494</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>237155</t>
+          <t>254494</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>237155</t>
+          <t>254494</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>193210</t>
+          <t>211009</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>193210</t>
+          <t>211009</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>193210</t>
+          <t>211009</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>430365</t>
+          <t>465503</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>430365</t>
+          <t>465503</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>430365</t>
+          <t>465503</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>487349</t>
+          <t>518337</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>294204</t>
+          <t>480198</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>587316</t>
+          <t>556779</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>234424</t>
+          <t>247139</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>209671</t>
+          <t>224465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258198</t>
+          <t>275724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>721773</t>
+          <t>765476</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>549260</t>
+          <t>718829</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>809727</t>
+          <t>812747</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1179579</t>
+          <t>1024527</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1079612</t>
+          <t>986085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1372724</t>
+          <t>1062666</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>735179</t>
+          <t>806258</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711405</t>
+          <t>777673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>759932</t>
+          <t>828932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1914757</t>
+          <t>1830786</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1826803</t>
+          <t>1783515</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2087270</t>
+          <t>1877433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>72,31%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1666928</t>
+          <t>1542864</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1666928</t>
+          <t>1542864</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1666928</t>
+          <t>1542864</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>969603</t>
+          <t>1053397</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>969603</t>
+          <t>1053397</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>969603</t>
+          <t>1053397</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2636530</t>
+          <t>2596262</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2636530</t>
+          <t>2596262</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2636530</t>
+          <t>2596262</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
